--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-828491</t>
+          <t>I-203631</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.994704</t>
+          <t>-18.0460766</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.252159</t>
+          <t>-70.2496178</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Av Jorge Basadre con Av Tarata</t>
+          <t>Avenida Municipal / Calle Ricardo Palma</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-210432</t>
+          <t>I-461335</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-18.0332926</t>
+          <t>-18.0552698</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.2780792</t>
+          <t>-70.2432494</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Litoral / Dos</t>
+          <t>Calle César Faucheux / Prolongación Avenida Municipal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-348617</t>
+          <t>I-469057</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-18.0888527</t>
+          <t>-18.0329963</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.2868345</t>
+          <t>-70.2777657</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle 44 / Calle B8</t>
+          <t>Avenida Litoral / Tres</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-348932</t>
+          <t>I-469754</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-18.0890657</t>
+          <t>-18.0300542</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.2864767</t>
+          <t>-70.2704842</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle B9 / Prolongación Avenida Municipal</t>
+          <t>Avenida Cristo Rey / Avenida María Parado de Bellido</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-348983</t>
+          <t>I-471747</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ALTO DE LA ALIANZA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-18.0887324</t>
+          <t>-17.9875398</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.2872277</t>
+          <t>-70.2440929</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle 44 / Calle B7</t>
+          <t>Avenida Internacional / Calle José de la Riva Aguero</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-469045</t>
+          <t>I-472371</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230104</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-18.0317297</t>
+          <t>-17.9784501</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.2728248</t>
+          <t>-70.2371953</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Mariano Santos Mateo / Avenida Nora Flores Torres</t>
+          <t>Avenida Maria Parado de Bellido / Avenida Mariano Necochea</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-469046</t>
+          <t>I-472501</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230104</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-18.0316767</t>
+          <t>-17.9817031</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.2727817</t>
+          <t>-70.2352832</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Nora Flores Torres</t>
+          <t>Avenida Internacional / Pasaje Juan Manuel Iturregui</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-469056</t>
+          <t>I-731699</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230104</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-18.0330637</t>
+          <t>-17.9815667</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.2776967</t>
+          <t>-70.2349105</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Litoral / Tres</t>
+          <t>Avenida Internacional / Avenida Maria Parado de Bellido</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-469057</t>
+          <t>I-745672</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230104</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,22 +919,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-18.0329963</t>
+          <t>-17.9817506</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.2777657</t>
+          <t>-70.2257641</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Litoral / Tres</t>
+          <t>Avenida Artesanal A / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-469754</t>
+          <t>I-828491</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-18.0300542</t>
+          <t>-17.994704</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.2704842</t>
+          <t>-70.252159</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Cristo Rey / Avenida María Parado de Bellido</t>
+          <t>Calle Eduardo Pérez Gamboa / Calle Takana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-470846</t>
+          <t>I-86933</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ALTO DE LA ALIANZA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-18.0102213</t>
+          <t>-17.9841457</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.2457924</t>
+          <t>-70.24424</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida San Martín / Calle General Vizquerra / Calle Moquegua</t>
+          <t>Avenida Gregorio Albarracín / Calle Víctor Fajardo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-471273</t>
+          <t>I-86823</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ALTO DE LA ALIANZA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.9972897</t>
+          <t>-17.9889955</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.2400422</t>
+          <t>-70.2466071</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Industrial</t>
+          <t>Avenida Internacional / Calle Haití</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-471275</t>
+          <t>I-86949</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ALTO DE LA ALIANZA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-17.9970687</t>
+          <t>-17.9875015</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.2400783</t>
+          <t>-70.2474041</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Gregorio Albarracín / Calle Haití</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-632876</t>
+          <t>I-471594</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1179,27 +1179,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ALTO DE LA ALIANZA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-18.0301847</t>
+          <t>-17.9926381</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.2702811</t>
+          <t>-70.2502285</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Cristo Rey</t>
+          <t>Avenida Internacional / Jirón de la Unión</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-640092</t>
+          <t>I-203111</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1231,27 +1231,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-18.0302173</t>
+          <t>-18.0573631</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.2706388</t>
+          <t>-70.2567809</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida La Cultura / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-640093</t>
+          <t>I-86055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-18.0303524</t>
+          <t>-18.0313561</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.2707439</t>
+          <t>-70.2731678</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Nora Flores Torres / Calle 24 de Enero / Tacna</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-640094</t>
+          <t>I-86141</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,22 +1340,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-18.0300328</t>
+          <t>-18.014253</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.2705175</t>
+          <t>-70.2492356</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Cristo Rey</t>
+          <t>Avenida Francisco Bolognesi / Calle Ayacucho</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-640095</t>
+          <t>I-305953</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-18.0302894</t>
+          <t>-18.0117971</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.270499</t>
+          <t>-70.2464564</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Francisco Bolognesi / Calle Junín</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-640096</t>
+          <t>I-471153</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-18.0301051</t>
+          <t>-18.0025606</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.2708048</t>
+          <t>-70.2373144</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Augusto Bernardino Leguía / Calle Cajamarca</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>l-640097</t>
+          <t>I-472636</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230104</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,27 +1491,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-18.0299501</t>
+          <t>-17.9799784</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.2710341</t>
+          <t>-70.2325603</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Internacional / Calle Hermanos Angulo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>l-640098</t>
+          <t>I-471194</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1548,961 +1548,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-18.030223</t>
+          <t>-18.0002029</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-70.2708864</t>
+          <t>-70.2449139</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Gustavo Pinto / Calle Amazonas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-640099</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-18.0301116</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-70.2710543</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>l-640101</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-18.029927</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-70.2706815</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Avenida Cristo Rey</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-640102</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-18.0297676</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-70.2709287</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Avenida Cristo Rey</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-714148</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-18.0101828</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-70.24569</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Avenida San Martín</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-714149</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-18.0104366</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-70.2462208</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Avenida San Martín</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-744537</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-17.996996</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-70.2399534</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>l-744538</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-17.9970096</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-70.2398865</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>l-768981</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-18.0315869</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-70.2729012</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Avenida Nora Flores Torres</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>l-85567</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-17.997173</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-70.240057</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Avenida Industrial</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>l-85579</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-17.9971328</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-70.2398098</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Avenida Industrial</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>l-85944</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-18.0331358</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-70.2776187</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Avenida Litoral / Tres</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>l-85954</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-18.0332952</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-70.2777823</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Avenida José Gálvez / Avenida Litoral</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>l-86055</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-18.0313561</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-70.2731678</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Avenida Nora Flores Torres / Calle 24 de Enero / Tacna</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>l-86106</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-18.0174335</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-70.2540204</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Avenida Miguel Grau / Calle Huancavelica</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>l-86516</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-18.0297214</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-70.2710041</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Avenida Cristo Rey / Calle Rufino Albarracín</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>l-86660</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-18.0171801</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-70.2542372</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Avenida Miguel Grau / Calle Huancavelica</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>l-86839</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-18.0038201</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-70.2580752</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Avenida Industrial / Avenida Jorge Basadre Grohmann / Calle Hipolito Unanue</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>l-86853</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-18.0039119</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-70.2581548</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Avenida Industrial / Avenida Jorge Basadre Grohmann</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
         <is>
           <t>230101</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Municipal / Calle Ricardo Palma</t>
+          <t>Avenida Municipal / Calle Cristóbal Colón / Calle Ricardo Palma</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle Eduardo Pérez Gamboa / Calle Takana</t>
+          <t>Avenida Jorge Basadre Grohmann / Avenida Tarata / Calle Eduardo Pérez Gamboa</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi / Calle Ayacucho</t>
+          <t>Avenida Billinghurst / Avenida Francisco Bolognesi / Calle Ayacucho</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Gustavo Pinto / Calle Amazonas</t>
+          <t>Avenida Gustavo Pinto / Calle Alianza / Calle Amazonas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1567,6 +1567,58 @@
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>230101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-472608</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-17.9823508</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-70.2362508</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Avenida Internacional / Pasaje Juan Espinoza Medrano</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>230101</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-203631</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>230110</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-18.0460766</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-461335</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>230110</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-18.0552698</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-469057</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-18.0329963</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-469754</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-18.0300542</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-471747</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-17.9875398</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-472371</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-17.9784501</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-472501</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-17.9817031</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-731699</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-17.9815667</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-745672</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-17.9817506</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-828491</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-17.994704</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-86933</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-17.9841457</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-86823</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-17.9889955</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-86949</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-17.9875015</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-471594</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-17.9926381</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-203111</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>230110</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-18.0573631</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-86055</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-18.0313561</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-86141</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-18.014253</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-305953</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-18.0117971</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-471153</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-18.0025606</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-472636</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-17.9799784</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-471194</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-18.0002029</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-472608</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-17.9823508</t>
@@ -1616,11 +1506,6 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-TACNA.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-203631</t>
+          <t>I-86949</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-18.0460766</t>
+          <t>-17.9875015</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.2496178</t>
+          <t>-70.2474041</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Municipal / Calle Cristóbal Colón / Calle Ricardo Palma</t>
+          <t>Avenida Gregorio Albarracín / Calle Haití</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-461335</t>
+          <t>I-86933</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-18.0552698</t>
+          <t>-17.9841457</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.2432494</t>
+          <t>-70.24424</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle César Faucheux / Prolongación Avenida Municipal</t>
+          <t>Avenida Gregorio Albarracín / Calle Víctor Fajardo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-469057</t>
+          <t>I-86823</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-18.0329963</t>
+          <t>-17.9889955</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.2777657</t>
+          <t>-70.2466071</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Litoral / Tres</t>
+          <t>Avenida Internacional / Calle Haití</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-469754</t>
+          <t>I-86141</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-18.0300542</t>
+          <t>-18.014253</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.2704842</t>
+          <t>-70.2492356</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Cristo Rey / Avenida María Parado de Bellido</t>
+          <t>Avenida Francisco Bolognesi / Calle Ayacucho</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-471747</t>
+          <t>I-86055</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-17.9875398</t>
+          <t>-18.0313561</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.2440929</t>
+          <t>-70.2731678</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Calle José de la Riva Aguero</t>
+          <t>Avenida Nora Flores Torres / Calle 24 de Enero / Tacna</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-472371</t>
+          <t>I-828491</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-17.9784501</t>
+          <t>-17.994704</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.2371953</t>
+          <t>-70.252159</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Maria Parado de Bellido / Avenida Mariano Necochea</t>
+          <t>Calle Eduardo Pérez Gamboa / Calle Takana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-472501</t>
+          <t>I-745672</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-17.9817031</t>
+          <t>-17.9817506</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.2352832</t>
+          <t>-70.2257641</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Pasaje Juan Manuel Iturregui</t>
+          <t>Avenida Artesanal A / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-745672</t>
+          <t>I-472636</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-17.9817506</t>
+          <t>-17.9799784</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.2257641</t>
+          <t>-70.2325603</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Artesanal A / Calle s / n</t>
+          <t>Avenida Internacional / Calle Hermanos Angulo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,27 +909,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-828491</t>
+          <t>I-472608</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.994704</t>
+          <t>-17.9823508</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.252159</t>
+          <t>-70.2362508</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Jorge Basadre Grohmann / Avenida Tarata / Calle Eduardo Pérez Gamboa</t>
+          <t>Avenida Internacional / Pasaje Juan Espinoza Medrano</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-86933</t>
+          <t>I-472501</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-17.9841457</t>
+          <t>-17.9817031</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.24424</t>
+          <t>-70.2352832</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Gregorio Albarracín / Calle Víctor Fajardo</t>
+          <t>Avenida Internacional / Pasaje Juan Manuel Iturregui</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-86823</t>
+          <t>I-472371</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.9889955</t>
+          <t>-17.9784501</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.2466071</t>
+          <t>-70.2371953</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Calle Haití</t>
+          <t>Avenida Maria Parado de Bellido / Avenida Mariano Necochea</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-86949</t>
+          <t>I-471747</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-17.9875015</t>
+          <t>-17.9875398</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.2474041</t>
+          <t>-70.2440929</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Gregorio Albarracín / Calle Haití</t>
+          <t>Avenida Internacional / Calle José de la Riva Aguero</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-203111</t>
+          <t>I-471194</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-18.0573631</t>
+          <t>-18.0002029</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.2567809</t>
+          <t>-70.2449139</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida La Cultura / Calle s / n</t>
+          <t>Avenida Gustavo Pinto / Calle Amazonas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1191,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-86055</t>
+          <t>I-471153</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-18.0313561</t>
+          <t>-18.0025606</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.2731678</t>
+          <t>-70.2373144</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Nora Flores Torres / Calle 24 de Enero / Tacna</t>
+          <t>Avenida Augusto Bernardino Leguía / Calle Cajamarca</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1238,27 +1238,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-86141</t>
+          <t>I-469754</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-18.014253</t>
+          <t>-18.0300542</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.2492356</t>
+          <t>-70.2704842</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Billinghurst / Avenida Francisco Bolognesi / Calle Ayacucho</t>
+          <t>Avenida Cristo Rey / Avenida María Parado de Bellido</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-305953</t>
+          <t>I-469057</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-18.0117971</t>
+          <t>-18.0329963</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.2464564</t>
+          <t>-70.2777657</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi / Calle Junín</t>
+          <t>Avenida Litoral / Tres</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-471153</t>
+          <t>I-461335</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-18.0025606</t>
+          <t>-18.0552698</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.2373144</t>
+          <t>-70.2432494</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida Augusto Bernardino Leguía / Calle Cajamarca</t>
+          <t>Calle César Faucheux / Prolongación Avenida Municipal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-472636</t>
+          <t>I-305953</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-17.9799784</t>
+          <t>-18.0117971</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.2325603</t>
+          <t>-70.2464564</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Calle Hermanos Angulo</t>
+          <t>Avenida Francisco Bolognesi / Calle Junín</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-471194</t>
+          <t>I-203631</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-18.0002029</t>
+          <t>-18.0460766</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-70.2449139</t>
+          <t>-70.2496178</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Gustavo Pinto / Calle Alianza / Calle Amazonas</t>
+          <t>Avenida Municipal / Calle Ricardo Palma</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-472608</t>
+          <t>I-203111</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-17.9823508</t>
+          <t>-18.0573631</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-70.2362508</t>
+          <t>-70.2567809</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Pasaje Juan Espinoza Medrano</t>
+          <t>Avenida La Cultura / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
